--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11F96D04-A68B-4BFD-880A-34E95107224E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E74AAD5C-C54B-42AF-A3C9-EC5258CF7D88}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B049AEAC-7B83-46E0-881A-5DB2DAC47EDF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{847408B6-DC0F-482F-BC59-C91A9AD0A074}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFB05441-02A4-4D0B-BD38-157CC303895C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{973FED17-AD4F-4074-9CB5-98555DB59261}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E74AAD5C-C54B-42AF-A3C9-EC5258CF7D88}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0D2BAB5-A255-44D9-A6CF-348051A3A76F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{847408B6-DC0F-482F-BC59-C91A9AD0A074}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D91A3A08-7AB0-47F6-B95E-05A267E7375E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{973FED17-AD4F-4074-9CB5-98555DB59261}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF205E7D-94D4-4992-8A1C-6721C5F28406}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0D2BAB5-A255-44D9-A6CF-348051A3A76F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FADC3BCF-A9B2-42BD-AD71-3C5B76772DC1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D91A3A08-7AB0-47F6-B95E-05A267E7375E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0FE71E2-E238-48B2-9D19-15E14773F08C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF205E7D-94D4-4992-8A1C-6721C5F28406}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{795F93B5-8A01-485D-BFD0-37DA58B0BF85}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1430,22 +1430,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E74AAD5C-C54B-42AF-A3C9-EC5258CF7D88}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB124AF0-E600-4074-9A26-C694027D5EFB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{847408B6-DC0F-482F-BC59-C91A9AD0A074}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF73D034-C403-48C4-8987-CD4FDA80A068}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{973FED17-AD4F-4074-9CB5-98555DB59261}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C0BB8AD-4E69-4744-A5C2-65E75374D669}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1430,22 +1430,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FADC3BCF-A9B2-42BD-AD71-3C5B76772DC1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AD70ADB-590B-426F-B156-FECDF7F18722}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0FE71E2-E238-48B2-9D19-15E14773F08C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6802F370-9020-4ACC-B3ED-3143624F229F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{795F93B5-8A01-485D-BFD0-37DA58B0BF85}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB827F55-A1CA-4526-AA22-DE218EEB707F}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AD70ADB-590B-426F-B156-FECDF7F18722}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7978942E-02D0-4F89-AC5A-B0CD681C75DC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6802F370-9020-4ACC-B3ED-3143624F229F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B6D7517-6B31-4BF7-AEF6-0AF55BA0D115}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB827F55-A1CA-4526-AA22-DE218EEB707F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF6DA8BF-8D8F-4305-B0E9-48F9642385DA}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7978942E-02D0-4F89-AC5A-B0CD681C75DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A55E3266-5875-4DF6-920C-0639A1FEEC50}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B6D7517-6B31-4BF7-AEF6-0AF55BA0D115}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD113880-219A-4A77-9AA4-777C8162A89E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF6DA8BF-8D8F-4305-B0E9-48F9642385DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6680D31E-E27E-4D87-BDB8-C9C7B9C80405}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A55E3266-5875-4DF6-920C-0639A1FEEC50}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2836AD9C-1B17-4ACD-AB0A-CECDE37995EE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD113880-219A-4A77-9AA4-777C8162A89E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BBC9E4-02EE-4E88-891E-43AED16E4F60}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6680D31E-E27E-4D87-BDB8-C9C7B9C80405}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{735D1EC7-37EB-4061-BEC7-880C4D6C1C8E}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2836AD9C-1B17-4ACD-AB0A-CECDE37995EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE485BBA-9BFB-4C9A-AE7A-2AC0BC507A41}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BBC9E4-02EE-4E88-891E-43AED16E4F60}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C2A976D-0CEE-4E50-A5A3-1E3C634EF475}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{735D1EC7-37EB-4061-BEC7-880C4D6C1C8E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B8AC52C-847A-4E1F-AD99-A4EB1373A37F}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE485BBA-9BFB-4C9A-AE7A-2AC0BC507A41}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD729F23-2F73-42DC-B30E-968FAE1A6762}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C2A976D-0CEE-4E50-A5A3-1E3C634EF475}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5188F0BB-4505-4B95-A068-BCDBD8FBBC12}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B8AC52C-847A-4E1F-AD99-A4EB1373A37F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08820410-73E9-4F88-8629-0727D2116550}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD729F23-2F73-42DC-B30E-968FAE1A6762}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD15746E-448A-4622-A078-3821075B9174}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5188F0BB-4505-4B95-A068-BCDBD8FBBC12}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{047FEC92-52C0-4A78-AC4C-2D0365579F3C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08820410-73E9-4F88-8629-0727D2116550}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ACC1E2F-5B6C-4A01-99EC-5A8B739C0F69}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD15746E-448A-4622-A078-3821075B9174}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B773749B-19C3-408E-9ECC-8932BBB55687}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{047FEC92-52C0-4A78-AC4C-2D0365579F3C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AADA062E-4349-4222-99B1-F0FF0995D3A2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ACC1E2F-5B6C-4A01-99EC-5A8B739C0F69}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B60CC66-1F42-4FC6-966A-345C189FF592}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B773749B-19C3-408E-9ECC-8932BBB55687}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05119B93-5B34-4B1C-8458-E501A0F3CAAA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AADA062E-4349-4222-99B1-F0FF0995D3A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CDFB144-2050-4185-81A4-EA4252AD3BED}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B60CC66-1F42-4FC6-966A-345C189FF592}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{600F31EA-326B-4397-B912-50839B1EC8AA}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05119B93-5B34-4B1C-8458-E501A0F3CAAA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9A00868-713D-4BEB-BBDE-EF360773C991}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CDFB144-2050-4185-81A4-EA4252AD3BED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A463A6F5-0271-43CE-B834-B99A33C776D0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{600F31EA-326B-4397-B912-50839B1EC8AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE20C97A-03B7-4E58-95B3-6CD9A7A465EC}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9A00868-713D-4BEB-BBDE-EF360773C991}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6939DAE9-8A30-40DD-A4B6-9DF4E4B4AE26}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A463A6F5-0271-43CE-B834-B99A33C776D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E0F8AAD-FDE1-400A-9729-186013936F69}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE20C97A-03B7-4E58-95B3-6CD9A7A465EC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAC3F194-022D-4656-9405-4B3C9C5E0FF3}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6939DAE9-8A30-40DD-A4B6-9DF4E4B4AE26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0093EFFC-A89E-4DE5-BE18-DBA9AD081365}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E0F8AAD-FDE1-400A-9729-186013936F69}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FDA3293-E32E-463C-BBCA-9320CA631C1C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAC3F194-022D-4656-9405-4B3C9C5E0FF3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CB798D7-10AC-4BEB-8B72-809DCE1B0324}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0093EFFC-A89E-4DE5-BE18-DBA9AD081365}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C5844A-2A25-4B3A-A23E-A93739F7B7B2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FDA3293-E32E-463C-BBCA-9320CA631C1C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BC4AAA6-FF9F-47E8-BD37-C4B1D953A63E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CB798D7-10AC-4BEB-8B72-809DCE1B0324}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89C9DDCD-02CB-49E6-ADCE-8D916F813939}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C5844A-2A25-4B3A-A23E-A93739F7B7B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80E19924-26AD-4324-BFA9-C2DC46BB762E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BC4AAA6-FF9F-47E8-BD37-C4B1D953A63E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51C6D83A-0BA3-4D35-B200-EDF34049D910}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89C9DDCD-02CB-49E6-ADCE-8D916F813939}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{198EB100-6BE9-44E8-8728-0CCDCC2717EE}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80E19924-26AD-4324-BFA9-C2DC46BB762E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CCE5FAE-4365-4FEA-8868-7FD7CBD47E4B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51C6D83A-0BA3-4D35-B200-EDF34049D910}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41D2F3DA-3323-4060-86D5-F2E473012EE3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{198EB100-6BE9-44E8-8728-0CCDCC2717EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BA8418E-65CB-4520-8F81-C8A013A6065C}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CCE5FAE-4365-4FEA-8868-7FD7CBD47E4B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F98CEB9-E1C3-46E3-B0E4-0F30227FBC67}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41D2F3DA-3323-4060-86D5-F2E473012EE3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE601E30-90CA-4365-B064-FC0936DC23ED}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BA8418E-65CB-4520-8F81-C8A013A6065C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A52A04FA-6A94-42AA-93F3-049B8DE0A09E}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F98CEB9-E1C3-46E3-B0E4-0F30227FBC67}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF670EAD-05E0-4186-8C51-1DBFD6125CDA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE601E30-90CA-4365-B064-FC0936DC23ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71F2D5C3-4CF6-4AF2-9927-087387D82F78}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A52A04FA-6A94-42AA-93F3-049B8DE0A09E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1F5DBA0-D9AB-452E-A6FC-307BA113D6C8}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF670EAD-05E0-4186-8C51-1DBFD6125CDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D87C44E1-4291-464F-9FD6-0D2E268B492A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71F2D5C3-4CF6-4AF2-9927-087387D82F78}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AD0E929-6BA3-4C78-8CC5-9CA3BEE1499E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1F5DBA0-D9AB-452E-A6FC-307BA113D6C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E0A333-0CAA-470D-B849-E1CFF178AE26}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D87C44E1-4291-464F-9FD6-0D2E268B492A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DF5294C-F253-4623-B45B-4A839C6DD239}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AD0E929-6BA3-4C78-8CC5-9CA3BEE1499E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18323B4E-7DA2-4C2C-B5F7-A213737E7D64}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E0A333-0CAA-470D-B849-E1CFF178AE26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{377816D1-FD32-4D94-BB04-CD9774F64A65}"/>
 </file>
--- a/____EvoM1_TraitTable/manipulation.xlsx
+++ b/____EvoM1_TraitTable/manipulation.xlsx
@@ -1439,13 +1439,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DF5294C-F253-4623-B45B-4A839C6DD239}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F199131-9436-49CA-AFC6-00DC2F012DBA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18323B4E-7DA2-4C2C-B5F7-A213737E7D64}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96786EC8-B561-492B-B39E-E45135002700}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{377816D1-FD32-4D94-BB04-CD9774F64A65}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F87E3CA7-CC08-4415-97A4-786B4FAA3E27}"/>
 </file>